--- a/inputs/stage1_sample_input.xlsx
+++ b/inputs/stage1_sample_input.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns2="http://schemas.libreoffice.org/" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
@@ -11,11 +11,12 @@
     <sheet name="Planning" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Fleet" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Clusters" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="DayAheadMarketPrices" sheetId="4" r:id="rId7" state="visible"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <ns2:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1124,4 +1125,225 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>price_eur_per_kwh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="n">
+        <v>44569.291666666664</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>0.280000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="n">
+        <v>44569.302083333336</v>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>0.270000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>44569.312500000000</v>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>0.260000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>44569.322916666664</v>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>0.240000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>44569.333333333336</v>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.220000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="n">
+        <v>44569.343750000000</v>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.200000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="n">
+        <v>44569.354166666664</v>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>0.180000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>44569.364583333336</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.160000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="n">
+        <v>44569.375000000000</v>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>0.150000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="n">
+        <v>44569.385416666664</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>0.140000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>44569.395833333336</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>0.130000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>44569.406250000000</v>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>0.120000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="n">
+        <v>44569.416666666664</v>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.110000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>44569.427083333336</v>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>0.100000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>44569.437500000000</v>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>0.110000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>44569.447916666664</v>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.120000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>44569.458333333336</v>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.140000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>44569.468750000000</v>
+      </c>
+      <c r="B19" s="1" t="n">
+        <v>0.160000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>44569.479166666664</v>
+      </c>
+      <c r="B20" s="1" t="n">
+        <v>0.180000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="n">
+        <v>44569.489583333336</v>
+      </c>
+      <c r="B21" s="1" t="n">
+        <v>0.200000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="n">
+        <v>44569.500000000000</v>
+      </c>
+      <c r="B22" s="1" t="n">
+        <v>0.220000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="n">
+        <v>44569.510416666664</v>
+      </c>
+      <c r="B23" s="1" t="n">
+        <v>0.240000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="n">
+        <v>44569.520833333336</v>
+      </c>
+      <c r="B24" s="1" t="n">
+        <v>0.260000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="n">
+        <v>44569.531250000000</v>
+      </c>
+      <c r="B25" s="1" t="n">
+        <v>0.280000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>